--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_09-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_09-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.49205</v>
+        <v>16.7808</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1229</v>
+        <v>16.43918</v>
       </c>
       <c r="E2" t="n">
-        <v>16.077</v>
+        <v>16.54071</v>
       </c>
       <c r="F2" t="n">
-        <v>42.25728</v>
+        <v>42.39395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05061</v>
+        <v>0.05044</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8133</v>
+        <v>1.79352</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67574</v>
+        <v>16.78614</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49037</v>
+        <v>16.56803</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47215</v>
+        <v>16.7389</v>
       </c>
       <c r="F3" t="n">
-        <v>42.48186</v>
+        <v>42.43127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05077</v>
+        <v>0.05009</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7812</v>
+        <v>1.77655</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.64409</v>
+        <v>16.31291</v>
       </c>
       <c r="D4" t="n">
-        <v>16.20334</v>
+        <v>16.2233</v>
       </c>
       <c r="E4" t="n">
-        <v>16.60717</v>
+        <v>16.2853</v>
       </c>
       <c r="F4" t="n">
-        <v>42.43376</v>
+        <v>42.41052</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05026</v>
+        <v>0.05094</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79935</v>
+        <v>1.77265</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.60893</v>
+        <v>16.36739</v>
       </c>
       <c r="D5" t="n">
-        <v>16.64584</v>
+        <v>16.18881</v>
       </c>
       <c r="E5" t="n">
-        <v>16.33017</v>
+        <v>16.30732</v>
       </c>
       <c r="F5" t="n">
-        <v>42.19105</v>
+        <v>42.00875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05042</v>
+        <v>0.04952</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83949</v>
+        <v>1.78549</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.80771</v>
+        <v>16.59983</v>
       </c>
       <c r="D6" t="n">
-        <v>16.09294</v>
+        <v>16.21876</v>
       </c>
       <c r="E6" t="n">
-        <v>16.65281</v>
+        <v>16.42617</v>
       </c>
       <c r="F6" t="n">
-        <v>41.98936</v>
+        <v>41.7787</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0505</v>
+        <v>0.04991</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81215</v>
+        <v>1.79127</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66023</v>
+        <v>16.7283</v>
       </c>
       <c r="D7" t="n">
-        <v>16.32906</v>
+        <v>16.42899</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47341</v>
+        <v>16.51605</v>
       </c>
       <c r="F7" t="n">
-        <v>42.19194</v>
+        <v>41.48877</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04882</v>
+        <v>0.05025</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84499</v>
+        <v>1.80253</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.74524</v>
+        <v>16.93599</v>
       </c>
       <c r="D8" t="n">
-        <v>16.33367</v>
+        <v>16.41845</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52259</v>
+        <v>16.55977</v>
       </c>
       <c r="F8" t="n">
-        <v>42.40429</v>
+        <v>42.2884</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0496</v>
+        <v>0.04922</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78459</v>
+        <v>1.77758</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.65277</v>
+        <v>16.68453</v>
       </c>
       <c r="D9" t="n">
-        <v>16.57336</v>
+        <v>16.34724</v>
       </c>
       <c r="E9" t="n">
-        <v>16.68178</v>
+        <v>16.58539</v>
       </c>
       <c r="F9" t="n">
-        <v>41.86732</v>
+        <v>42.15171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05028</v>
+        <v>0.0495</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79452</v>
+        <v>1.79661</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.42367</v>
+        <v>16.42639</v>
       </c>
       <c r="D10" t="n">
-        <v>16.09505</v>
+        <v>16.14006</v>
       </c>
       <c r="E10" t="n">
-        <v>16.38996</v>
+        <v>16.22533</v>
       </c>
       <c r="F10" t="n">
-        <v>42.26426</v>
+        <v>41.08358</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05028</v>
+        <v>0.0493</v>
       </c>
       <c r="H10" t="n">
-        <v>1.78679</v>
+        <v>1.81178</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59905</v>
+        <v>0.60346</v>
       </c>
       <c r="D12" t="n">
-        <v>1.08321</v>
+        <v>1.07916</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60902</v>
+        <v>0.59768</v>
       </c>
       <c r="D13" t="n">
-        <v>1.11162</v>
+        <v>1.10364</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59223</v>
+        <v>0.5928600000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09466</v>
+        <v>1.07955</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5883</v>
+        <v>0.59335</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10743</v>
+        <v>1.10498</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60408</v>
+        <v>0.58693</v>
       </c>
       <c r="D16" t="n">
-        <v>1.09618</v>
+        <v>1.10098</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5947</v>
+        <v>0.60929</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10013</v>
+        <v>1.10782</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61273</v>
+        <v>0.60546</v>
       </c>
       <c r="D18" t="n">
-        <v>1.09717</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60136</v>
+        <v>0.61393</v>
       </c>
       <c r="D19" t="n">
-        <v>1.10358</v>
+        <v>1.0912</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.61087</v>
+        <v>0.60833</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10676</v>
+        <v>1.1032</v>
       </c>
     </row>
   </sheetData>
